--- a/templates/repair.xlsx
+++ b/templates/repair.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
   <si>
     <t>JESEAN PRINTER &amp; COMPUTER SPECIALISTS</t>
   </si>
@@ -36,18 +36,6 @@
   </si>
   <si>
     <t>BILLING STATEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIT </t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL </t>
   </si>
   <si>
     <t>Received the above unit in good order and condition.</t>
@@ -67,24 +55,12 @@
   <si>
     <t>JOB ORDER</t>
   </si>
-  <si>
-    <t>CUSTOMER:   AFTECH                                                                                                                                                  DATE: 5/26/2026</t>
-  </si>
-  <si>
-    <t>BROTHER SN:E80729H2H419791</t>
-  </si>
-  <si>
-    <t>PRINTHEAD REPLACEMENT</t>
-  </si>
-  <si>
-    <t>LABOR</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,24 +112,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FF434343"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF434343"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -178,20 +136,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="6"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <color rgb="FF000000"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,82 +146,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFD9"/>
-        <bgColor rgb="FFE2EFD9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -307,85 +188,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -830,18 +675,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -860,18 +705,18 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -890,18 +735,18 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -948,18 +793,18 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -978,18 +823,18 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1006,18 +851,18 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1034,18 +879,18 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1062,18 +907,18 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1090,18 +935,18 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1118,18 +963,18 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1146,18 +991,18 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1174,18 +1019,18 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1202,18 +1047,18 @@
       <c r="Z13" s="2"/>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -1230,18 +1075,18 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -1262,14 +1107,14 @@
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="30" t="s">
-        <v>8</v>
+      <c r="E16" s="20" t="s">
+        <v>4</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1316,20 +1161,20 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>9</v>
+      <c r="A18" s="10" t="s">
+        <v>5</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="4"/>
       <c r="F18" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1348,20 +1193,20 @@
       <c r="Z18" s="2"/>
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
-        <v>11</v>
+      <c r="A19" s="14" t="s">
+        <v>7</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="32" t="s">
-        <v>12</v>
+      <c r="G19" s="15" t="s">
+        <v>8</v>
       </c>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1436,18 +1281,18 @@
       <c r="Z21" s="2"/>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1466,18 +1311,18 @@
       <c r="Z22" s="2"/>
     </row>
     <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -1496,18 +1341,18 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -1554,18 +1399,18 @@
       <c r="Z25" s="2"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
-        <v>13</v>
+      <c r="A26" s="21" t="s">
+        <v>9</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1583,19 +1428,17 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1614,22 +1457,16 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="J28" s="18"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -1647,23 +1484,17 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12">
-        <v>4150</v>
-      </c>
-      <c r="J29" s="11"/>
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -1681,21 +1512,17 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="21"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12">
-        <v>350</v>
-      </c>
-      <c r="J30" s="11"/>
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -1712,17 +1539,17 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -1740,17 +1567,17 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="21"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -1768,17 +1595,17 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="21"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="11"/>
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -1796,17 +1623,17 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="21"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="11"/>
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -1824,17 +1651,17 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="21"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
@@ -1852,22 +1679,17 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="27"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="28">
-        <f>SUM(I29:J35)</f>
-        <v>4500</v>
-      </c>
-      <c r="J36" s="18"/>
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -1914,20 +1736,20 @@
       <c r="Z37" s="2"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
-        <v>9</v>
+      <c r="A38" s="10" t="s">
+        <v>5</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
       <c r="E38" s="4"/>
       <c r="F38" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
-      <c r="G38" s="31"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -1946,20 +1768,20 @@
       <c r="Z38" s="2"/>
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
-        <v>11</v>
+      <c r="A39" s="14" t="s">
+        <v>7</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
-      <c r="G39" s="32" t="s">
-        <v>12</v>
+      <c r="G39" s="15" t="s">
+        <v>8</v>
       </c>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -11779,6 +11601,63 @@
     </row>
   </sheetData>
   <mergeCells count="73">
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="G18:J18"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="A39:D39"/>
@@ -11795,63 +11674,6 @@
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="E16:J16"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
